--- a/data/numeric/input/data_217/2025-11-04_11：27-_11：42_NH3.xlsx
+++ b/data/numeric/input/data_217/2025-11-04_11：27-_11：42_NH3.xlsx
@@ -28882,18 +28882,26 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
+  <documentManagement>
+    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B1A5FFA-D523-4CE6-AB57-84D23BA96102}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB318E1D-A024-4389-82E1-E79BFAFDF2FF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3040FDAA-FE6C-4139-99E2-6A1CF51F09C5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EC7D231B-5358-4CAC-B86D-737D367AFF8C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F0B40403-332C-4F8D-8BEE-59DDBEFDFD98}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{40B9BA28-AB67-42E7-83CF-0FE90AE35EE6}"/>
 </file>